--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -41,54 +41,60 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mixed Types</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DateTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>def</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Only blanks</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Numbers with integers</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Numers without integers</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Errors</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DateTime with num</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text with long text</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>Only blanks</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Numbers with integers</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Numers without integers</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text with long text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DateTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DateTime with num</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Errors</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mixed Types</x:t>
-  </x:si>
-  <x:si>
     <x:t>Value</x:t>
   </x:si>
   <x:si>
-    <x:t>ABC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyzabcdefghijklmnopqrstuvwxyz</x:t>
-  </x:si>
-  <x:si>
     <x:t>Content of the table is not important. All fields must be used, in order to save values as shared items</x:t>
   </x:si>
   <x:si>
+    <x:t>(blank)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Column Labels</x:t>
   </x:si>
   <x:si>
@@ -104,9 +110,6 @@
     <x:t>12/24/2020 Total</x:t>
   </x:si>
   <x:si>
-    <x:t>(blank)</x:t>
-  </x:si>
-  <x:si>
     <x:t>(blank) Total</x:t>
   </x:si>
   <x:si>
@@ -116,6 +119,15 @@
     <x:t>45000 Total</x:t>
   </x:si>
   <x:si>
+    <x:t>#N/A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#DIV/0!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#REF!</x:t>
+  </x:si>
+  <x:si>
     <x:t>10 Total</x:t>
   </x:si>
   <x:si>
@@ -131,22 +143,10 @@
     <x:t>ABC Total</x:t>
   </x:si>
   <x:si>
-    <x:t>#DIV/0!</x:t>
-  </x:si>
-  <x:si>
     <x:t>#DIV/0! Total</x:t>
   </x:si>
   <x:si>
     <x:t>8/10/2020 Total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Row Labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#N/A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#REF!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1085,39 +1085,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="F1" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>0</x:v>
@@ -1126,10 +1126,10 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="1">
         <x:v>1</x:v>
@@ -1143,7 +1143,7 @@
     </x:row>
     <x:row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>1</x:v>
@@ -1152,10 +1152,10 @@
         <x:v>14.4</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="14">
         <x:v>1.52083333333333</x:v>
@@ -1172,7 +1172,7 @@
     </x:row>
     <x:row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>1</x:v>
@@ -1181,10 +1181,10 @@
         <x:v>14.4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G4" s="1">
         <x:v>44189</x:v>
@@ -1201,7 +1201,7 @@
     </x:row>
     <x:row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="3">
         <x:v>0.6875</x:v>
@@ -1218,7 +1218,7 @@
     </x:row>
     <x:row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="3">
         <x:v>0.6875</x:v>
@@ -1233,29 +1233,29 @@
     </x:row>
     <x:row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>45000</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="e">
         <x:v>#DIV/0!</x:v>
@@ -1263,7 +1263,7 @@
     </x:row>
     <x:row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="1">
         <x:v>44053</x:v>
@@ -1271,7 +1271,7 @@
     </x:row>
     <x:row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <x:c r="A11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="2">
         <x:v>0.6875</x:v>
@@ -1326,12 +1326,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <x:c r="A1" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="B3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1339,31 +1339,31 @@
         <x:v>0.6875</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L4" s="13">
         <x:v>1.52083333333333</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P4" s="1">
         <x:v>44189</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AG4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1371,43 +1371,43 @@
         <x:v>0.6875</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H5" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L5" s="13">
         <x:v>1.52083333333333</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P5" s="1">
         <x:v>44189</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T5" s="0">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="V5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="W5" s="0">
         <x:v>45000</x:v>
       </x:c>
       <x:c r="Y5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="Z5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AF5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1415,106 +1415,106 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>14.5</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Z6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="T6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="U6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="W6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="X6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Z6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="AA6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AB6" s="12">
         <x:v>0.6875</x:v>
       </x:c>
       <x:c r="AC6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AD6" s="1">
         <x:v>44053</x:v>
       </x:c>
       <x:c r="AE6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="T7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Z7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AB7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AD7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A8" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1529,12 +1529,12 @@
     </x:row>
     <x:row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A12" s="10" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A13" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1549,42 +1549,42 @@
     </x:row>
     <x:row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A16" s="10" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A17" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A18" s="10" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A19" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A20" s="8" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A21" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A22" s="10" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <x:c r="A23" s="11" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -1066,69 +1066,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{D06156F0-4807-4DF1-B293-641447249403}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:J11"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.855469" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="21.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="23.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="6" width="15" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="18.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="9" max="9" width="15" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.285156" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="12.855469" customWidth="1"/>
+    <x:col min="3" max="3" width="21.710938" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="23.570312" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="6" width="15" customWidth="1"/>
+    <x:col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="18.710938" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="15" customWidth="1"/>
+    <x:col min="10" max="10" width="13.285156" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E1" s="0" t="s">
+      <x:c r="E1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F1" s="0" t="s">
+      <x:c r="F1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G1" s="0" t="s">
+      <x:c r="G1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H1" s="0" t="s">
+      <x:c r="H1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I1" s="0" t="s">
+      <x:c r="I1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J1" s="0" t="s">
+      <x:c r="J1" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="E2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="1">
@@ -1142,19 +1139,19 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="C3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3">
         <x:v>14.4</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="F3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="14">
@@ -1166,24 +1163,24 @@
       <x:c r="I3" s="1" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="b">
+      <x:c r="J3" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="C4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4">
         <x:v>14.4</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="E4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="F4" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="G4" s="1">
@@ -1195,12 +1192,12 @@
       <x:c r="I4" s="1" t="e">
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="b">
+      <x:c r="J4" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="A5" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="3">
@@ -1212,12 +1209,12 @@
       <x:c r="I5" s="3" t="e">
         <x:v>#N/A</x:v>
       </x:c>
-      <x:c r="J5" s="0">
+      <x:c r="J5">
         <x:v>14.5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="A6" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="3">
@@ -1227,42 +1224,42 @@
         <x:v>0.6875</x:v>
       </x:c>
       <x:c r="I6" s="3"/>
-      <x:c r="J6" s="0">
+      <x:c r="J6">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="A7" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H7" s="0">
+      <x:c r="H7">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
+      <x:c r="J7" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="A8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="0">
+      <x:c r="H8">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="J8" s="0" t="s">
+      <x:c r="J8" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A9" s="0" t="s">
+      <x:c r="A9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J9" s="0" t="e">
+      <x:c r="J9" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A10" s="0" t="s">
+      <x:c r="A10" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="1">
@@ -1270,7 +1267,7 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <x:c r="A11" s="0" t="s">
+      <x:c r="A11" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="2">
@@ -1278,50 +1275,44 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{361B2662-EEFD-42EE-88B5-C353D88DBC9B}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:AG23"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="255" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="16.285156" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="7.855469" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="6.855469" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="9.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="7" width="15.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="10.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="9" max="9" width="12.140625" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="10" max="11" width="13.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="12" max="12" width="15.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="10.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="14" max="15" width="18.855469" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="16" max="16" width="12.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="17" max="17" width="10.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="18" max="19" width="15.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="20" max="20" width="9.140625" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="21" max="21" width="9.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="22" max="22" width="8.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="23" max="23" width="7.855469" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="24" max="24" width="9.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="25" max="25" width="10.855469" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="26" max="26" width="9.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="27" max="27" width="12.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="28" max="28" width="12.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="29" max="29" width="15.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="30" max="30" width="11.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="31" max="31" width="14.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="32" max="33" width="12.140625" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="255" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.285156" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="7.855469" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="6.855469" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="9.425781" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="7" width="15.570312" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="10.570312" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="11" width="13.710938" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="15.710938" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="10.425781" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="15" width="18.855469" bestFit="1" customWidth="1"/>
+    <x:col min="16" max="16" width="12.570312" bestFit="1" customWidth="1"/>
+    <x:col min="17" max="17" width="10.425781" bestFit="1" customWidth="1"/>
+    <x:col min="18" max="19" width="15.710938" bestFit="1" customWidth="1"/>
+    <x:col min="20" max="20" width="9.140625" bestFit="1" customWidth="1"/>
+    <x:col min="21" max="21" width="9.425781" bestFit="1" customWidth="1"/>
+    <x:col min="22" max="22" width="8.425781" bestFit="1" customWidth="1"/>
+    <x:col min="23" max="23" width="7.855469" bestFit="1" customWidth="1"/>
+    <x:col min="24" max="24" width="9.425781" bestFit="1" customWidth="1"/>
+    <x:col min="25" max="25" width="10.855469" bestFit="1" customWidth="1"/>
+    <x:col min="26" max="26" width="9.570312" bestFit="1" customWidth="1"/>
+    <x:col min="27" max="27" width="12.570312" bestFit="1" customWidth="1"/>
+    <x:col min="28" max="28" width="12.425781" bestFit="1" customWidth="1"/>
+    <x:col min="29" max="29" width="15.570312" bestFit="1" customWidth="1"/>
+    <x:col min="30" max="30" width="11.570312" bestFit="1" customWidth="1"/>
+    <x:col min="31" max="31" width="14.710938" bestFit="1" customWidth="1"/>
+    <x:col min="32" max="33" width="12.140625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
@@ -1330,7 +1321,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -1338,31 +1329,31 @@
       <x:c r="B4" s="12">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="G4" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="K4" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="L4" s="13">
         <x:v>1.52083333333333</x:v>
       </x:c>
-      <x:c r="O4" s="0" t="s">
+      <x:c r="O4" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="P4" s="1">
         <x:v>44189</x:v>
       </x:c>
-      <x:c r="S4" s="0" t="s">
+      <x:c r="S4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="T4" s="0" t="s">
+      <x:c r="T4" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="AG4" s="0" t="s">
+      <x:c r="AG4" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -1370,140 +1361,140 @@
       <x:c r="B5" s="12">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="F5" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H5" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
+      <x:c r="J5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="L5" s="13">
         <x:v>1.52083333333333</x:v>
       </x:c>
-      <x:c r="N5" s="0" t="s">
+      <x:c r="N5" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="P5" s="1">
         <x:v>44189</x:v>
       </x:c>
-      <x:c r="R5" s="0" t="s">
+      <x:c r="R5" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="T5" s="0">
+      <x:c r="T5">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="V5" s="0" t="s">
+      <x:c r="V5" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="W5" s="0">
+      <x:c r="W5">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="Y5" s="0" t="s">
+      <x:c r="Y5" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="Z5" s="0" t="s">
+      <x:c r="Z5" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="AF5" s="0" t="s">
+      <x:c r="AF5" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>14.5</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="E6" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H6" s="0" t="s">
+      <x:c r="H6" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s">
+      <x:c r="I6" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L6" s="0" t="s">
+      <x:c r="L6" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="M6" s="0" t="s">
+      <x:c r="M6" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
+      <x:c r="P6" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="Q6" s="0" t="s">
+      <x:c r="Q6" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="T6" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U6" s="0" t="s">
+      <x:c r="T6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U6" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="W6" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X6" s="0" t="s">
+      <x:c r="W6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X6" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="Z6" s="0" t="s">
+      <x:c r="Z6" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="AA6" s="0" t="s">
+      <x:c r="AA6" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB6" s="12">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="AC6" s="0" t="s">
+      <x:c r="AC6" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AD6" s="1">
         <x:v>44053</x:v>
       </x:c>
-      <x:c r="AE6" s="0" t="s">
+      <x:c r="AE6" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="A7" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="H7" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="L7" s="0" t="s">
+      <x:c r="L7" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="P7" s="0" t="s">
+      <x:c r="P7" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="T7" s="0" t="s">
+      <x:c r="T7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="W7" s="0" t="s">
+      <x:c r="W7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Z7" s="0" t="s">
+      <x:c r="Z7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="AB7" s="0" t="s">
+      <x:c r="AB7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="AD7" s="0" t="s">
+      <x:c r="AD7" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -1588,10 +1579,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId2"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup orientation="portrait" r:id="rId2"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -1069,15 +1069,14 @@
   <x:dimension ref="A1:J11"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="12.855469" customWidth="1"/>
-    <x:col min="3" max="3" width="21.710938" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="23.570312" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <x:col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
     <x:col min="5" max="6" width="15" customWidth="1"/>
     <x:col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="18.710938" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="15" customWidth="1"/>
-    <x:col min="10" max="10" width="13.285156" customWidth="1"/>
+    <x:col min="10" max="10" width="13.28515625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1286,32 +1285,32 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="255" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="16.285156" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="7.855469" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="6.855469" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="9.425781" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="7" width="15.570312" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="10.570312" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <x:col min="10" max="11" width="13.710938" bestFit="1" customWidth="1"/>
-    <x:col min="12" max="12" width="15.710938" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="10.425781" bestFit="1" customWidth="1"/>
-    <x:col min="14" max="15" width="18.855469" bestFit="1" customWidth="1"/>
-    <x:col min="16" max="16" width="12.570312" bestFit="1" customWidth="1"/>
-    <x:col min="17" max="17" width="10.425781" bestFit="1" customWidth="1"/>
-    <x:col min="18" max="19" width="15.710938" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="15" width="18.85546875" bestFit="1" customWidth="1"/>
+    <x:col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="18" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
     <x:col min="20" max="20" width="9.140625" bestFit="1" customWidth="1"/>
-    <x:col min="21" max="21" width="9.425781" bestFit="1" customWidth="1"/>
-    <x:col min="22" max="22" width="8.425781" bestFit="1" customWidth="1"/>
-    <x:col min="23" max="23" width="7.855469" bestFit="1" customWidth="1"/>
-    <x:col min="24" max="24" width="9.425781" bestFit="1" customWidth="1"/>
-    <x:col min="25" max="25" width="10.855469" bestFit="1" customWidth="1"/>
-    <x:col min="26" max="26" width="9.570312" bestFit="1" customWidth="1"/>
-    <x:col min="27" max="27" width="12.570312" bestFit="1" customWidth="1"/>
-    <x:col min="28" max="28" width="12.425781" bestFit="1" customWidth="1"/>
-    <x:col min="29" max="29" width="15.570312" bestFit="1" customWidth="1"/>
-    <x:col min="30" max="30" width="11.570312" bestFit="1" customWidth="1"/>
-    <x:col min="31" max="31" width="14.710938" bestFit="1" customWidth="1"/>
+    <x:col min="21" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="22" max="22" width="8.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="23" max="23" width="7.85546875" bestFit="1" customWidth="1"/>
+    <x:col min="24" max="24" width="9.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
+    <x:col min="26" max="26" width="9.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="27" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="28" max="28" width="12.42578125" bestFit="1" customWidth="1"/>
+    <x:col min="29" max="29" width="15.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="30" max="30" width="11.5703125" bestFit="1" customWidth="1"/>
+    <x:col min="31" max="31" width="14.7109375" bestFit="1" customWidth="1"/>
     <x:col min="32" max="33" width="12.140625" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -1154,10 +1154,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="14">
-        <x:v>1.52083333333333</x:v>
+        <x:v>1.5208333333333335</x:v>
       </x:c>
       <x:c r="H3" s="14">
-        <x:v>1.52083333333333</x:v>
+        <x:v>1.5208333333333335</x:v>
       </x:c>
       <x:c r="I3" s="1" t="e">
         <x:v>#DIV/0!</x:v>
@@ -1338,7 +1338,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L4" s="13">
-        <x:v>1.52083333333333</x:v>
+        <x:v>1.5208333333333335</x:v>
       </x:c>
       <x:c r="O4" t="s">
         <x:v>21</x:v>
@@ -1370,7 +1370,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L5" s="13">
-        <x:v>1.52083333333333</x:v>
+        <x:v>1.5208333333333335</x:v>
       </x:c>
       <x:c r="N5" t="s">
         <x:v>21</x:v>
